--- a/it_forms/033_software_request_form--it_forms.xlsx
+++ b/it_forms/033_software_request_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,64 +520,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>software_request_form_1</t>
+          <t>software_request_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Software Request Form</t>
+          <t>What is the software you are requesting?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>software_request_form_2</t>
+          <t>software_category_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Software Request Form</t>
+          <t>Software Category</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>software_category</t>
+          <t>software_sub_category_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Software Category</t>
+          <t>Software Sub Category</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>software_sub_category</t>
+          <t>software_description_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Software Sub Category</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Brief Description</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of the software you are requesting</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +616,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>software_description</t>
+          <t>software_version_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Software Description</t>
+          <t>Software Version</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,41 +639,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>software_version</t>
+          <t>contact_information_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Software Version</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide your name and contact phone number and email so we can reach you</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>department_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>is_urgent_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact Phone</t>
+          <t>Is this software request an urgent matter?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,63 +707,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>software_timeline_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Contact Email</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Expected Timeline</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide a rough timeline for when you would like the software to be implemented</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>department_name</t>
+          <t>primary_user_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Department Name</t>
+          <t>Primary User</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>department_name_1</t>
+          <t>software_note_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Department Name</t>
+          <t>Additional Information (if needed)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,292 +785,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>department_name_2</t>
+          <t>notification_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Department Name</t>
+          <t>Would you like to be notified when the software is ready to use?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>software_request_form_14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>software_request_form_15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>software_request_form_16</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>software_request_form_17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>software_request_form_18</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>software_request_form_19</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>software_request_form_20</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>software_request_form_21</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>software_request_form_22</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>software_request_form_23</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>software_request_form_24</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>software_request_form_25</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Software Request Form</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,12 +811,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,34 +839,323 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>software_category_choices</t>
+          <t>software_category_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>General</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>software_category_choices</t>
+          <t>software_category_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>software_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>software_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Network</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>software_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>software_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>operating_system</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Operating System</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>software_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>software_sub_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>category_a</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Category A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>software_sub_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>category_b</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Category B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>software_sub_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>category_c</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Category C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>software_sub_category_1_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>department_1_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>department_1_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>security</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>department_1_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>department_1_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>department_1_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>primary_user_1_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>me</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Me</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>primary_user_1_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>another_user</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Another User</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>primary_user_1_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Team</t>
         </is>
       </c>
     </row>
